--- a/import-specification/devices/meteo.xlsx
+++ b/import-specification/devices/meteo.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="130">
   <si>
     <t>Field Type</t>
   </si>
@@ -288,6 +288,15 @@
   </si>
   <si>
     <t>Maximum wind speed</t>
+  </si>
+  <si>
+    <t>R_ISO</t>
+  </si>
+  <si>
+    <t>kOhm</t>
+  </si>
+  <si>
+    <t>Isolation resistance</t>
   </si>
   <si>
     <t>SLI[1..x]</t>
@@ -747,7 +756,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="16.425" bestFit="true" customWidth="true" style="0"/>
@@ -1244,10 +1253,10 @@
         <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1255,13 +1264,13 @@
         <v>38</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
         <v>43</v>
       </c>
       <c r="D33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1269,10 +1278,10 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="D34" t="s">
         <v>97</v>
@@ -1300,10 +1309,10 @@
         <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1311,13 +1320,13 @@
         <v>38</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1325,13 +1334,13 @@
         <v>38</v>
       </c>
       <c r="B38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1339,10 +1348,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="D39" t="s">
         <v>109</v>
@@ -1356,10 +1365,10 @@
         <v>110</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="D40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1367,13 +1376,13 @@
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C41" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1381,10 +1390,10 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="D42" t="s">
         <v>116</v>
@@ -1411,16 +1420,19 @@
       <c r="B44" t="s">
         <v>120</v>
       </c>
+      <c r="C44" t="s">
+        <v>121</v>
+      </c>
+      <c r="D44" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
         <v>38</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
-      </c>
-      <c r="D45" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1428,10 +1440,10 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D46" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1439,10 +1451,21 @@
         <v>38</v>
       </c>
       <c r="B47" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D47" t="s">
-        <v>126</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
